--- a/data/google_news_dedup_audit_17_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_17_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,31 +445,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9126003980636597</v>
+        <v>0.9027184247970581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Four Seasons Hotel London at Park Lane to unveil new suites - Boutique Hotelier</t>
+          <t>A trick to get free delivery on Amazon | Money newsletter - revolutionradio.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Four Seasons Hotel London at Park Lane Unveils Newly Renovated Suites This May - Hospitality Net</t>
+          <t>A trick to get free delivery on Amazon | Money newsletter - Roch Valley Radio</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="n">
         <v>5</v>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>0.8301641941070557</v>
@@ -487,31 +487,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7512016296386719</v>
+        <v>0.9846278429031372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A trick to get free delivery on Amazon | Money newsletter - revolutionradio.com</t>
+          <t>Thief intercepts $25K silver bar delivery from FedEx in Rockville - WJLA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>A trick to get free delivery on Amazon | Money newsletter - This is the Coast</t>
+          <t>Thief intercepts $25K silver bar delivery from FedEx in Rockville - WBFF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>0.771195650100708</v>
@@ -529,337 +529,547 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9876582026481628</v>
+        <v>0.8213443756103516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tiental wagens beschadigd na explosie in Sint-Gillis: al tweede incident op enkele dagen tijd - HBVL</t>
+          <t>IOC ups auto LPG supply by 300% - The Times of India</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tiental wagens beschadigd na explosie in Sint-Gillis: al tweede incident op enkele dagen tijd - Nieuwsblad</t>
+          <t>IOC ups auto LPG supply by 300% - MSN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9920600652694702</v>
+        <v>0.9755096435546875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Explosie en beschietingen aan zelfde woning in Sint-Gillis: burgemeester vraagt hulp aan minister van Binnenlandse Zaken - VRT</t>
+          <t>“Moet ik misschien met een kogelvrij vest slapen?”: 83-jarige Fernande beleeft schrik van haar leven na zware explosie in Sint-Gillis - HLN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Explosie en beschietingen aan zelfde woning in Sint-Gillis: burgemeester vraagt hulp aan minister van Binnenlandse Zaken - MSN</t>
+          <t>“Moet ik misschien met een kogelvrij vest slapen?”: 83-jarige Fernande beleeft schrik van haar leven na zware explosie in Sint-Gillis | Foto - HLN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9755096435546875</v>
+        <v>0.7374228239059448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>“Moet ik misschien met een kogelvrij vest slapen?”: 83-jarige Fernande beleeft schrik van haar leven na zware explosie in Sint-Gillis - HLN</t>
+          <t>Schietpartij in Landgraaf: geen gewonden, politie houdt twee personen aan - De Limburger</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>“Moet ik misschien met een kogelvrij vest slapen?”: 83-jarige Fernande beleeft schrik van haar leven na zware explosie in Sint-Gillis | Foto - HLN</t>
+          <t>Landgraaf schrikt op van knallen met gasalarmpistool: politie houdt twee personen aan - De Limburger</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7374228239059448</v>
+        <v>0.9899109601974487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Schietpartij in Landgraaf: geen gewonden, politie houdt twee personen aan - De Limburger</t>
+          <t>Parket vraagt 4 jaar cel voor duo na aanslag in Plataanstraat: “We zijn die nacht niet eens in België geweest” - GVA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Landgraaf schrikt op van knallen met gasalarmpistool: politie houdt twee personen aan - De Limburger</t>
+          <t>Parket vraagt 4 jaar cel voor duo na aanslag in Plataanstraat: “We zijn die nacht niet eens in België geweest” - Nieuwsblad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9899109601974487</v>
+        <v>0.8147057294845581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Parket vraagt 4 jaar cel voor duo na aanslag in Plataanstraat: “We zijn die nacht niet eens in België geweest” - GVA</t>
+          <t>Agression au couteau boulevard Anspach à Bruxelles - MSN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Parket vraagt 4 jaar cel voor duo na aanslag in Plataanstraat: “We zijn die nacht niet eens in België geweest” - Nieuwsblad</t>
+          <t>Un sans-abri violemment agressé boulevard Poincaré à Bruxelles - BruxellesToday</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7085422277450562</v>
+        <v>0.7063390016555786</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Russia issues bomb threat to four UK locations including London, Suffolk and Leicester - lbc.co.uk</t>
+          <t>Patrick Bruel visé par une enquête en Belgique après la plainte d’une attachée de presse pour agression sexuelle - Gentside</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Russia makes direct strike threat to three areas in UK - LADbible</t>
+          <t>"La gent féminine est une proie pour Patrick Bruel" : une attachée de presse qui accuse le chanteur d'agression témoigne - magicmaman.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7435553073883057</v>
+        <v>0.5707810521125793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Russia issues bomb threat to four UK locations including London, Suffolk and Leicester - lbc.co.uk</t>
+          <t>Drei alkoholisierte E-Scooter-Lenker sind heute Nacht in Ingolstadt aufgeflogen - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Is the UK at War with Russia? London, Leicester, and Suffolk Named on 'Hit List' of European Strike Targets - International Business Times UK</t>
+          <t>Betrunken auf E-Scooter unterwegs: Verfahren gegen mehrere Männer - Augsburger Allgemeine</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B13" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7636851072311401</v>
+        <v>0.7575448751449585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>What is needed for next week's London Tube strike to be called off? - Metro.co.uk</t>
+          <t>Drei alkoholisierte E-Scooter-Lenker sind heute Nacht in Ingolstadt aufgeflogen - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Six days of tube strikes on the London Underground will start next week - Time Out</t>
+          <t>Ingolstadt: E-Scooter-Fahrer mit Alkohol erwischt - Augsburger Allgemeine</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B14" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7740689516067505</v>
+        <v>0.7085422277450562</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>What is needed for next week's London Tube strike to be called off? - Metro.co.uk</t>
+          <t>Russia issues bomb threat to four UK locations including London, Suffolk and Leicester - lbc.co.uk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>How to beat the Tube strike: All the lines running next week - London Evening Standard</t>
+          <t>Russia makes direct strike threat to three areas in UK - LADbible</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B15" t="n">
         <v>75</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7015551328659058</v>
+        <v>0.6963458061218262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>What is needed for next week's London Tube strike to be called off? - Metro.co.uk</t>
+          <t>London Tube Strike to disrupt services next week - RailAdvent</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>London Tube and Bus strike dates, routes and times for April 2026 - lbc.co.uk</t>
+          <t>'Call off the Tube strikes,' bosses urge as RMT union threatens £210 million blow to London - London Evening Standard</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B16" t="n">
         <v>76</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6932096481323242</v>
+        <v>0.8153756856918335</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>London Tube Strike to disrupt services next week - RailAdvent</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>What is needed for next week's London Tube strike to be called off? - Metro.co.uk</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>London Tube and bus strikes to spark four days of travel chaos next week as two major lines to shut - London Evening Standard</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B17" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8032518029212952</v>
+        <v>0.7429715991020203</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sciopero dei bus a Milano (e non solo), a rischio gli interscambi: gli orari dello stop - MilanoToday</t>
+          <t>London Tube Strike to disrupt services next week - RailAdvent</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sciopero trasporti in arrivo: bus fermi a Milano, Monza Brianza, Lodi e Pavia. Le fasce orarie - MilanoToday</t>
+          <t>Tube and bus strikes set to bring four days of travel chaos next week - London Evening Standard</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>73</v>
+      </c>
+      <c r="B18" t="n">
         <v>81</v>
       </c>
-      <c r="B18" t="n">
-        <v>84</v>
-      </c>
       <c r="C18" t="n">
-        <v>0.8025496602058411</v>
+        <v>0.7621090412139893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sciopero dei bus a Milano (e non solo), a rischio gli interscambi: gli orari dello stop - MilanoToday</t>
+          <t>London Tube Strike to disrupt services next week - RailAdvent</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sciopero dei bus a Milano, a rischio gli interscambi: la situazione - Moveo by Telepass</t>
+          <t>How to beat the Tube strike: All the lines running next week - London Evening Standard</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B19" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7381308674812317</v>
+        <v>0.6925122737884521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CGIL: manifestazione remigration a Milano contro i valori della Costituzione - Affaritaliani</t>
+          <t>Sciopero trasporti in arrivo: bus fermi a Milano, Monza Brianza, Lodi e Pavia. Le fasce orarie - MilanoToday</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Milano è "casa di molti popoli": così gli antagonisti si preparano contro il Remigration Summit in Duomo - MilanoToday</t>
+          <t>Sciopero dei bus a Milano, a rischio gli interscambi: la situazione - Moveo by Telepass</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" t="n">
         <v>90</v>
       </c>
       <c r="C20" t="n">
-        <v>0.718042254447937</v>
+        <v>0.8032519221305847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CGIL: manifestazione remigration a Milano contro i valori della Costituzione - Affaritaliani</t>
+          <t>Sciopero trasporti in arrivo: bus fermi a Milano, Monza Brianza, Lodi e Pavia. Le fasce orarie - MilanoToday</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Manifestazione Lega e Patrioti UE a Milano, la condanna della Presidente del Consiglio comunale - milanopavia.news</t>
+          <t>Sciopero dei bus a Milano (e non solo), a rischio gli interscambi: gli orari dello stop - MilanoToday</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" t="n">
+        <v>102</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6728419065475464</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sciopero trasporti in arrivo: bus fermi a Milano, Monza Brianza, Lodi e Pavia. Le fasce orarie - MilanoToday</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sabato di cortei e tensione a Milano: orari, percorsi e strade a rischio - MilanoToday</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>88</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.4659993350505829</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Tre cortei di protesta contro il Remigration Summit a Milano - RSI Radiotelevisione svizzera</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>88</v>
+      </c>
+      <c r="B23" t="n">
         <v>93</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.7003884315490723</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C23" t="n">
+        <v>0.5669167041778564</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>"Milano città aperta, nessuno spazio per l'odio": la manifestazione contro il Remigration Summit - Radio Lombardia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>88</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.4749071896076202</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>CGIL: manifestazione remigration a Milano contro i valori della Costituzione - Affaritaliani</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>88</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5811226367950439</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Milano è "casa di molti popoli": così gli antagonisti si preparano contro il Remigration Summit in Duomo - MilanoToday</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>88</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.5880504846572876</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Manifestazione Lega e Patrioti UE a Milano, la condanna della Presidente del Consiglio comunale - milanopavia.news</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>88</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.4765180349349976</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Palazzo Marino condanna il “Remigration Summit”: centrodestra diviso in Aula, FI si astiene - MilanoToday</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>88</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7360647916793823</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>La Lega di Savona a Milano per la manifestazione “Pace, Lavoro e Sicurezza” - IVG.it</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>88</v>
+      </c>
+      <c r="B29" t="n">
+        <v>105</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.5060651898384094</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Milano, tre cortei contro il Remigration Summit: da dove partono e il punto comune di arrivo - Il Giorno</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>88</v>
+      </c>
+      <c r="B30" t="n">
+        <v>107</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6121694445610046</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>Dopo le sconfitte della destra, Salvini si vergogna di dire che la manifestazione a Milano è per la remigrazione - Fanpage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>91</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7618688941001892</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sciopero giornalisti, il presidio a Milano: urgente rinnovo contratto - Quotidiano Nazionale</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Giornalisti in piazza a Milano: in 200 al presidio Alg per il rinnovo del contratto e condizioni di lavoro dignitose - Radio Lombardia</t>
         </is>
       </c>
     </row>
